--- a/stories/arbres/TREE-REL-005.xlsx
+++ b/stories/arbres/TREE-REL-005.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1301,6 +1318,11 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Dans la chambre, Maya a fait tomber la tour de Sami. Sami a les yeux mouillés. Maya a les joues chaudes. Maman est sur le lit. Papa passe dans le couloir. Maya dit pardon. Elle propose un geste. La peine reste un peu. On n'oblige pas l'amitié. Maman reste près.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1487,6 +1509,11 @@
         <v>8</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1649,6 +1676,11 @@
         <v>8</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Le matin, la tour de cubes tombe. C'est le matin. La couverture est toute douce. Maya s'approche, sans courir. Papa n'est pas loin. Maya dit pardon. Elle propose un geste. La peine reste un peu. On n'oblige pas l'amitié. Maman reste près.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1825,6 +1857,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Après une bêtise, que dit-on ? Avec le matin.</t>
         </is>
       </c>
     </row>
@@ -1993,6 +2030,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Maya dit pardon. Elle propose un geste. La peine reste un peu. On n'oblige pas l'amitié. Maman reste près. Maya retient le geste. Elle respire.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2179,6 +2221,11 @@
         <v>8</v>
       </c>
       <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2203,7 +2250,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Maya a choisi la cuisine, après le matin. Ça sent le savon de maman. Maya touche la cuisine tout doucement. Maman dit : je suis là. Maya dit pardon. Elle propose un geste. La peine reste un peu. On n'oblige pas l'amitié. Maman reste près.</t>
+          <t>Maya a choisi la cuisine, après le matin. Ça sent le savon de maman. Maya touche la cuisine tout doucement. Je suis là. Maya dit pardon. Elle propose un geste. La peine reste un peu. On n'oblige pas l'amitié. Maman reste près.</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -2341,6 +2388,13 @@
         <v>8</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Maya a choisi la cuisine, après le matin. Ça sent le savon de maman. Maya touche la cuisine tout doucement.
+maman|Je suis là.
+narrateur|Maya dit pardon. Elle propose un geste. La peine reste un peu. On n'oblige pas l'amitié. Maman reste près.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2527,6 +2581,11 @@
         <v>8</v>
       </c>
       <c r="AV9" s="2" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2689,6 +2748,11 @@
         <v>8</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Maya rejoint le ballon rouge, après le matin et la cuisine. La tasse est encore tiède. On dit merci. Maya dit pardon. Elle propose un geste. La peine reste un peu. On n'oblige pas l'amitié. Maman reste près. Maya pose le ballon rouge et va vers maman. Le soleil est encore là.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2851,6 +2915,11 @@
         <v>8</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3013,6 +3082,11 @@
         <v>8</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Maya rejoint le seau bleu, après le matin et la cuisine. Le parquet craque un tout petit peu. On écoute jusqu'au bout. Maya dit pardon. Elle propose un geste. La peine reste un peu. On n'oblige pas l'amitié. Maman reste près. Maya nomme encore le mot, tout bas. On gardu geste.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3175,6 +3249,11 @@
         <v>8</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3337,6 +3416,11 @@
         <v>8</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Maya rejoint le doudou, après le matin et la cuisine. Une abeille bourdonne loin. On attend un petit moment. Maya dit pardon. Elle propose un geste. La peine reste un peu. On n'oblige pas l'amitié. Maman reste près. Maya boit une gorgée. Elle se sent plus légère. Papa et maman sont là.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3499,6 +3583,11 @@
         <v>8</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3661,6 +3750,11 @@
         <v>8</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Maya a choisi le jardin, après le matin. Le lait est tiède. Près du jardin, Maya prend le temps. Pas de course. Maya dit pardon. Elle propose un geste. La peine reste un peu. On n'oblige pas l'amitié. Maman reste près.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3847,6 +3941,11 @@
         <v>8</v>
       </c>
       <c r="AV17" s="2" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4009,6 +4108,11 @@
         <v>8</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Maya rejoint le ballon rouge, après le matin et le jardin. Un gravier roule sous une semelle. On pose les fesses sur une chaise. Maya dit pardon. Elle propose un geste. La peine reste un peu. On n'oblige pas l'amitié. Maman reste près. Maya serre la main de maman, tout doux. On respire.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4171,6 +4275,11 @@
         <v>8</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4333,6 +4442,11 @@
         <v>8</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Maya rejoint le seau bleu, après le matin et le jardin. La fenêtre tremble un tout petit peu. On sourit un peu. Maya dit pardon. Elle propose un geste. La peine reste un peu. On n'oblige pas l'amitié. Maman reste près. Maya pose le seau bleu et va vers maman. Merci, et au dodo bientôt.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4495,6 +4609,11 @@
         <v>8</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4657,6 +4776,11 @@
         <v>8</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Maya rejoint le doudou, après le matin et le jardin. Ça sent le savon de maman. On boit une gorgée d'eau. Maya dit pardon. Elle propose un geste. La peine reste un peu. On n'oblige pas l'amitié. Maman reste près. Maya dit merci à maman. Papa sourit. Le jeu peut recommencer.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4819,6 +4943,11 @@
         <v>8</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4981,6 +5110,11 @@
         <v>8</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Maya a choisi la chambre, après le matin. Le sable colle un peu aux doigts. Maya range un peu autour de la chambre. Elle respire. Maya dit pardon. Elle propose un geste. La peine reste un peu. On n'oblige pas l'amitié. Maman reste près.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5167,6 +5301,11 @@
         <v>8</v>
       </c>
       <c r="AV25" s="2" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5329,6 +5468,11 @@
         <v>8</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Maya rejoint le ballon rouge, après le matin et la chambre. Un pigeon roucoule. On essuie une miette. Maya dit pardon. Elle propose un geste. La peine reste un peu. On n'oblige pas l'amitié. Maman reste près. Maya nomme encore le mot, tout bas. On se serre un peu.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5491,6 +5635,11 @@
         <v>8</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5653,6 +5802,11 @@
         <v>8</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Maya rejoint le seau bleu, après le matin et la chambre. La cuillère tinte. On referme un livre. Maya dit pardon. Elle propose un geste. La peine reste un peu. On n'oblige pas l'amitié. Maman reste près. Maya serre la main de maman, tout doux. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5815,6 +5969,11 @@
         <v>8</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5977,6 +6136,11 @@
         <v>8</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Maya rejoint le doudou, après le matin et la chambre. Le ballon est un peu poudreux. On pose un jouet à sa place. Maya dit pardon. Elle propose un geste. La peine reste un peu. On n'oblige pas l'amitié. Maman reste près. Maya range le doudou un instant. Puis elle reprend, calme. La journée continue, tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6139,6 +6303,11 @@
         <v>8</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6301,6 +6470,11 @@
         <v>8</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Après la sieste, un dessin se froisse. Maya s'occupe de après la sieste. La cuillère tinte. Maman sourit. Maya dit pardon. Elle propose un geste. La peine reste un peu. On n'oblige pas l'amitié. Maman reste près.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6477,6 +6651,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|Après une bêtise, que dit-on ? Avec après la sieste.</t>
         </is>
       </c>
     </row>
@@ -6645,6 +6824,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Maya dit pardon. Elle propose un geste. La peine reste un peu. On n'oblige pas l'amitié. Maman reste près. Maya répète le mot. Maman hoche la tête.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6831,6 +7015,11 @@
         <v>8</v>
       </c>
       <c r="AV35" s="2" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -6993,6 +7182,11 @@
         <v>8</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Maya a choisi la cuisine, après la sieste. Le pain croustille. Maya montre la cuisine à maman. Elle nomme ce qu'elle sent. Maya dit pardon. Elle propose un geste. La peine reste un peu. On n'oblige pas l'amitié. Maman reste près.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7179,6 +7373,11 @@
         <v>8</v>
       </c>
       <c r="AV37" s="2" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7341,6 +7540,11 @@
         <v>8</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Maya rejoint le ballon rouge, après la sieste et la cuisine. Une goutte de pluie sèche déjà. On marche tout doucement. Maya dit pardon. Elle propose un geste. La peine reste un peu. On n'oblige pas l'amitié. Maman reste près. Maya dit merci à maman. Papa sourit. On se dit à plus tard.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7503,6 +7707,11 @@
         <v>8</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7665,6 +7874,11 @@
         <v>8</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Maya rejoint le seau bleu, après la sieste et la cuisine. Le banc est tiède. On se tait une seconde. Maya dit pardon. Elle propose un geste. La peine reste un peu. On n'oblige pas l'amitié. Maman reste près. Maya dit merci à maman. Papa sourit. Le soleil est encore là.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7827,6 +8041,11 @@
         <v>8</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -7989,6 +8208,11 @@
         <v>8</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Maya rejoint le doudou, après la sieste et la cuisine. Ça sent le savon des mains. On ouvre les mains, loin de l'autre. Maya dit pardon. Elle propose un geste. La peine reste un peu. On n'oblige pas l'amitié. Maman reste près. Maya dit merci à maman. Papa sourit. On gardu geste.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8151,6 +8375,11 @@
         <v>8</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8313,6 +8542,11 @@
         <v>8</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Maya a choisi le jardin, après la sieste. La corde de la balançoire bouge. Maya choisit le jardin. Papa n'est pas loin. Maya dit pardon. Elle propose un geste. La peine reste un peu. On n'oblige pas l'amitié. Maman reste près.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8499,6 +8733,11 @@
         <v>8</v>
       </c>
       <c r="AV45" s="2" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8661,6 +8900,11 @@
         <v>8</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Maya rejoint le ballon rouge, après la sieste et le jardin. Une feuille tourne et tombe. On s'assoit près de l'adulte. Maya dit pardon. Elle propose un geste. La peine reste un peu. On n'oblige pas l'amitié. Maman reste près. On laisse le ballon rouge à sa place. Maya est près de maman. Papa et maman sont là.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8823,6 +9067,11 @@
         <v>8</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -8985,6 +9234,11 @@
         <v>8</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Maya rejoint le seau bleu, après la sieste et le jardin. L'eau fait un tout petit bruit. On nomme ce qu'on sent. Maya dit pardon. Elle propose un geste. La peine reste un peu. On n'oblige pas l'amitié. Maman reste près. On laisse le seau bleu à sa place. Maya est près de maman. On respire.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9147,6 +9401,11 @@
         <v>8</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9309,6 +9568,11 @@
         <v>8</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Maya rejoint le doudou, après la sieste et le jardin. Le soleil chauffe un peu le nez. On reprend le jeu, plus calme. Maya dit pardon. Elle propose un geste. La peine reste un peu. On n'oblige pas l'amitié. Maman reste près. On laisse le doudou à sa place. Maya est près de maman. Merci, et au dodo bientôt.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9471,6 +9735,11 @@
         <v>8</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9495,7 +9764,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Maya a choisi la chambre, après la sieste. Le sable est un peu frais. Maya touche la chambre tout doucement. Maman dit : je suis là. Maya dit pardon. Elle propose un geste. La peine reste un peu. On n'oblige pas l'amitié. Maman reste près.</t>
+          <t>Maya a choisi la chambre, après la sieste. Le sable est un peu frais. Maya touche la chambre tout doucement. Je suis là. Maya dit pardon. Elle propose un geste. La peine reste un peu. On n'oblige pas l'amitié. Maman reste près.</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -9633,6 +9902,13 @@
         <v>8</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Maya a choisi la chambre, après la sieste. Le sable est un peu frais. Maya touche la chambre tout doucement.
+maman|Je suis là.
+narrateur|Maya dit pardon. Elle propose un geste. La peine reste un peu. On n'oblige pas l'amitié. Maman reste près.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9819,6 +10095,11 @@
         <v>8</v>
       </c>
       <c r="AV53" s="2" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -9981,6 +10262,11 @@
         <v>8</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Maya rejoint le ballon rouge, après la sieste et la chambre. Une plume vole. On range les chaussures. Maya dit pardon. Elle propose un geste. La peine reste un peu. On n'oblige pas l'amitié. Maman reste près. Maya boit une gorgée. Elle se sent plus légère. Le jeu peut recommencer.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10143,6 +10429,11 @@
         <v>8</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10305,6 +10596,11 @@
         <v>8</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Maya rejoint le seau bleu, après la sieste et la chambre. Le pain croustille. On met le doudou près de soi. Maya dit pardon. Elle propose un geste. La peine reste un peu. On n'oblige pas l'amitié. Maman reste près. Maya boit une gorgée. Elle se sent plus légère. On se serre un peu.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10467,6 +10763,11 @@
         <v>8</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10629,6 +10930,11 @@
         <v>8</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Maya rejoint le doudou, après la sieste et la chambre. La laine du doudou est douce. On écoute le cœur, tout doux. Maya dit pardon. Elle propose un geste. La peine reste un peu. On n'oblige pas l'amitié. Maman reste près. Maya boit une gorgée. Elle se sent plus légère. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10791,6 +11097,11 @@
         <v>8</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10953,6 +11264,11 @@
         <v>8</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Le soir, un doudou glisse du lit. Voilà le soir. La fenêtre tremble un tout petit peu. Maya pose les pieds par terre, près de maman. Maya dit pardon. Elle propose un geste. La peine reste un peu. On n'oblige pas l'amitié. Maman reste près.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11129,6 +11445,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|Après une bêtise, que dit-on ? Avec le soir.</t>
         </is>
       </c>
     </row>
@@ -11297,6 +11618,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Maya dit pardon. Elle propose un geste. La peine reste un peu. On n'oblige pas l'amitié. Maman reste près. Maya pose les pieds par terre. On continue, tout calme.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11483,6 +11809,11 @@
         <v>8</v>
       </c>
       <c r="AV63" s="2" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11507,7 +11838,7 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Maya a choisi la cuisine, après le soir. Le coussin est moelleux. Maya touche la cuisine tout doucement. Maman dit : je suis là. Maya dit pardon. Elle propose un geste. La peine reste un peu. On n'oblige pas l'amitié. Maman reste près.</t>
+          <t>Maya a choisi la cuisine, après le soir. Le coussin est moelleux. Maya touche la cuisine tout doucement. Je suis là. Maya dit pardon. Elle propose un geste. La peine reste un peu. On n'oblige pas l'amitié. Maman reste près.</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -11645,6 +11976,13 @@
         <v>8</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Maya a choisi la cuisine, après le soir. Le coussin est moelleux. Maya touche la cuisine tout doucement.
+maman|Je suis là.
+narrateur|Maya dit pardon. Elle propose un geste. La peine reste un peu. On n'oblige pas l'amitié. Maman reste près.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11831,6 +12169,11 @@
         <v>8</v>
       </c>
       <c r="AV65" s="2" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -11993,6 +12336,11 @@
         <v>8</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Maya rejoint le ballon rouge, après le soir et la cuisine. Un galet est lisse dans la main. On secoue les mains, loin. Maya dit pardon. Elle propose un geste. La peine reste un peu. On n'oblige pas l'amitié. Maman reste près. Maya serre la main de maman, tout doux. La journée continue, tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12155,6 +12503,11 @@
         <v>8</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12317,6 +12670,11 @@
         <v>8</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Maya rejoint le seau bleu, après le soir et la cuisine. Le train souffle au loin. On pose le sac. Maya dit pardon. Elle propose un geste. La peine reste un peu. On n'oblige pas l'amitié. Maman reste près. Maya boit une gorgée. Elle se sent plus légère. On se dit à plus tard.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12479,6 +12837,11 @@
         <v>8</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12503,7 +12866,7 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Maya rejoint le doudou, après le soir et la cuisine. Une vache meugle, loin. On dit le mot de l'émotion. Maya dit pardon. Elle propose un geste. La peine reste un peu. On n'oblige pas l'amitié. Maman reste près. Maman dit : je t'ai entendu. Papa aussi. Le soleil est encore là.</t>
+          <t>Maya rejoint le doudou, après le soir et la cuisine. Une vache meugle, loin. On dit le mot de l'émotion. Maya dit pardon. Elle propose un geste. La peine reste un peu. On n'oblige pas l'amitié. Maman reste près. Je t'ai entendu. Papa aussi. Le soleil est encore là.</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -12641,6 +13004,13 @@
         <v>8</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Maya rejoint le doudou, après le soir et la cuisine. Une vache meugle, loin. On dit le mot de l'émotion. Maya dit pardon. Elle propose un geste. La peine reste un peu. On n'oblige pas l'amitié. Maman reste près.
+maman|Je t'ai entendu. Papa aussi.
+narrateur|Le soleil est encore là.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12803,6 +13173,11 @@
         <v>8</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -12965,6 +13340,11 @@
         <v>8</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Maya a choisi le jardin, après le soir. Le sable est un peu frais. Le jardin reste à sa place. Maya aussi. Maya dit pardon. Elle propose un geste. La peine reste un peu. On n'oblige pas l'amitié. Maman reste près.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13151,6 +13531,11 @@
         <v>8</v>
       </c>
       <c r="AV73" s="2" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13313,6 +13698,11 @@
         <v>8</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Maya rejoint le ballon rouge, après le soir et le jardin. Un grillon chante, tout petit. On invite d'une petite voix. Maya dit pardon. Elle propose un geste. La peine reste un peu. On n'oblige pas l'amitié. Maman reste près. Maya pose le ballon rouge et va vers maman. On gardu geste.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13475,6 +13865,11 @@
         <v>8</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13637,6 +14032,11 @@
         <v>8</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Maya rejoint le seau bleu, après le soir et le jardin. Le bois de la table est lisse. On attend la réponse. Maya dit pardon. Elle propose un geste. La peine reste un peu. On n'oblige pas l'amitié. Maman reste près. Maya range le seau bleu un instant. Puis elle reprend, calme. Papa et maman sont là.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13799,6 +14199,11 @@
         <v>8</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -13961,6 +14366,11 @@
         <v>8</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Maya rejoint le doudou, après le soir et le jardin. Une goutte tombe dans l'évier. On propose une autre idée. Maya dit pardon. Elle propose un geste. La peine reste un peu. On n'oblige pas l'amitié. Maman reste près. On écoute le silence une seconde. Maya est assise. On respire.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14123,6 +14533,11 @@
         <v>8</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14285,6 +14700,11 @@
         <v>8</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Maya a choisi la chambre, après le soir. Ça sent le savon de maman. Maya range un peu autour de la chambre. Elle respire. Maya dit pardon. Elle propose un geste. La peine reste un peu. On n'oblige pas l'amitié. Maman reste près.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14471,6 +14891,11 @@
         <v>8</v>
       </c>
       <c r="AV81" s="2" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -14633,6 +15058,11 @@
         <v>8</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Maya rejoint le ballon rouge, après le soir et la chambre. Le toboggan est un peu froid. On va vers papa ou maman. Maya dit pardon. Elle propose un geste. La peine reste un peu. On n'oblige pas l'amitié. Maman reste près. Maya dit merci à maman. Papa sourit. Merci, et au dodo bientôt.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14795,6 +15225,11 @@
         <v>8</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -14957,6 +15392,11 @@
         <v>8</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Maya rejoint le seau bleu, après le soir et la chambre. La clochette de la porte tinte. On dit stop, tout clair. Maya dit pardon. Elle propose un geste. La peine reste un peu. On n'oblige pas l'amitié. Maman reste près. On laisse le seau bleu à sa place. Maya est près de maman. Le jeu peut recommencer.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15119,6 +15559,11 @@
         <v>8</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15281,6 +15726,11 @@
         <v>8</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Maya rejoint le doudou, après le soir et la chambre. Ça sent le thym du jardin. On s'éloigne d'un pas. Maya dit pardon. Elle propose un geste. La peine reste un peu. On n'oblige pas l'amitié. Maman reste près. Maya serre la main de maman, tout doux. On se serre un peu.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15443,6 +15893,11 @@
         <v>8</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15461,7 +15916,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15478,6 +15933,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-REL-005.xlsx
+++ b/stories/arbres/TREE-REL-005.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1323,6 +1328,7 @@
           <t>narrateur|Dans la chambre, Maya a fait tomber la tour de Sami. Sami a les yeux mouillés. Maya a les joues chaudes. Maman est sur le lit. Papa passe dans le couloir. Maya dit pardon. Elle propose un geste. La peine reste un peu. On n'oblige pas l'amitié. Maman reste près.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1514,6 +1520,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1681,6 +1688,7 @@
           <t>narrateur|Le matin, la tour de cubes tombe. C'est le matin. La couverture est toute douce. Maya s'approche, sans courir. Papa n'est pas loin. Maya dit pardon. Elle propose un geste. La peine reste un peu. On n'oblige pas l'amitié. Maman reste près.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1864,6 +1872,7 @@
           <t>narrateur|Après une bêtise, que dit-on ? Avec le matin.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2035,6 +2044,7 @@
           <t>narrateur|Oui. Maya dit pardon. Elle propose un geste. La peine reste un peu. On n'oblige pas l'amitié. Maman reste près. Maya retient le geste. Elle respire.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2226,6 +2236,7 @@
           <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2395,6 +2406,7 @@
 narrateur|Maya dit pardon. Elle propose un geste. La peine reste un peu. On n'oblige pas l'amitié. Maman reste près.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2586,6 +2598,7 @@
           <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2753,6 +2766,7 @@
           <t>narrateur|Maya rejoint le ballon rouge, après le matin et la cuisine. La tasse est encore tiède. On dit merci. Maya dit pardon. Elle propose un geste. La peine reste un peu. On n'oblige pas l'amitié. Maman reste près. Maya pose le ballon rouge et va vers maman. Le soleil est encore là.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2920,6 +2934,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3087,6 +3102,7 @@
           <t>narrateur|Maya rejoint le seau bleu, après le matin et la cuisine. Le parquet craque un tout petit peu. On écoute jusqu'au bout. Maya dit pardon. Elle propose un geste. La peine reste un peu. On n'oblige pas l'amitié. Maman reste près. Maya nomme encore le mot, tout bas. On gardu geste.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3254,6 +3270,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3421,6 +3438,7 @@
           <t>narrateur|Maya rejoint le doudou, après le matin et la cuisine. Une abeille bourdonne loin. On attend un petit moment. Maya dit pardon. Elle propose un geste. La peine reste un peu. On n'oblige pas l'amitié. Maman reste près. Maya boit une gorgée. Elle se sent plus légère. Papa et maman sont là.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3588,6 +3606,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3755,6 +3774,7 @@
           <t>narrateur|Maya a choisi le jardin, après le matin. Le lait est tiède. Près du jardin, Maya prend le temps. Pas de course. Maya dit pardon. Elle propose un geste. La peine reste un peu. On n'oblige pas l'amitié. Maman reste près.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3946,6 +3966,7 @@
           <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4113,6 +4134,7 @@
           <t>narrateur|Maya rejoint le ballon rouge, après le matin et le jardin. Un gravier roule sous une semelle. On pose les fesses sur une chaise. Maya dit pardon. Elle propose un geste. La peine reste un peu. On n'oblige pas l'amitié. Maman reste près. Maya serre la main de maman, tout doux. On respire.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4280,6 +4302,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4447,6 +4470,7 @@
           <t>narrateur|Maya rejoint le seau bleu, après le matin et le jardin. La fenêtre tremble un tout petit peu. On sourit un peu. Maya dit pardon. Elle propose un geste. La peine reste un peu. On n'oblige pas l'amitié. Maman reste près. Maya pose le seau bleu et va vers maman. Merci, et au dodo bientôt.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4614,6 +4638,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4781,6 +4806,7 @@
           <t>narrateur|Maya rejoint le doudou, après le matin et le jardin. Ça sent le savon de maman. On boit une gorgée d'eau. Maya dit pardon. Elle propose un geste. La peine reste un peu. On n'oblige pas l'amitié. Maman reste près. Maya dit merci à maman. Papa sourit. Le jeu peut recommencer.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4948,6 +4974,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5115,6 +5142,7 @@
           <t>narrateur|Maya a choisi la chambre, après le matin. Le sable colle un peu aux doigts. Maya range un peu autour de la chambre. Elle respire. Maya dit pardon. Elle propose un geste. La peine reste un peu. On n'oblige pas l'amitié. Maman reste près.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5306,6 +5334,7 @@
           <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5473,6 +5502,7 @@
           <t>narrateur|Maya rejoint le ballon rouge, après le matin et la chambre. Un pigeon roucoule. On essuie une miette. Maya dit pardon. Elle propose un geste. La peine reste un peu. On n'oblige pas l'amitié. Maman reste près. Maya nomme encore le mot, tout bas. On se serre un peu.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5640,6 +5670,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5807,6 +5838,7 @@
           <t>narrateur|Maya rejoint le seau bleu, après le matin et la chambre. La cuillère tinte. On referme un livre. Maya dit pardon. Elle propose un geste. La peine reste un peu. On n'oblige pas l'amitié. Maman reste près. Maya serre la main de maman, tout doux. On rentre.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5974,6 +6006,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6141,6 +6174,7 @@
           <t>narrateur|Maya rejoint le doudou, après le matin et la chambre. Le ballon est un peu poudreux. On pose un jouet à sa place. Maya dit pardon. Elle propose un geste. La peine reste un peu. On n'oblige pas l'amitié. Maman reste près. Maya range le doudou un instant. Puis elle reprend, calme. La journée continue, tout doux.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6308,6 +6342,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6475,6 +6510,7 @@
           <t>narrateur|Après la sieste, un dessin se froisse. Maya s'occupe de après la sieste. La cuillère tinte. Maman sourit. Maya dit pardon. Elle propose un geste. La peine reste un peu. On n'oblige pas l'amitié. Maman reste près.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6658,6 +6694,7 @@
           <t>narrateur|Après une bêtise, que dit-on ? Avec après la sieste.</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6829,6 +6866,7 @@
           <t>narrateur|Oui. Maya dit pardon. Elle propose un geste. La peine reste un peu. On n'oblige pas l'amitié. Maman reste près. Maya répète le mot. Maman hoche la tête.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7020,6 +7058,7 @@
           <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7187,6 +7226,7 @@
           <t>narrateur|Maya a choisi la cuisine, après la sieste. Le pain croustille. Maya montre la cuisine à maman. Elle nomme ce qu'elle sent. Maya dit pardon. Elle propose un geste. La peine reste un peu. On n'oblige pas l'amitié. Maman reste près.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7378,6 +7418,7 @@
           <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7545,6 +7586,7 @@
           <t>narrateur|Maya rejoint le ballon rouge, après la sieste et la cuisine. Une goutte de pluie sèche déjà. On marche tout doucement. Maya dit pardon. Elle propose un geste. La peine reste un peu. On n'oblige pas l'amitié. Maman reste près. Maya dit merci à maman. Papa sourit. On se dit à plus tard.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7712,6 +7754,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7879,6 +7922,7 @@
           <t>narrateur|Maya rejoint le seau bleu, après la sieste et la cuisine. Le banc est tiède. On se tait une seconde. Maya dit pardon. Elle propose un geste. La peine reste un peu. On n'oblige pas l'amitié. Maman reste près. Maya dit merci à maman. Papa sourit. Le soleil est encore là.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8046,6 +8090,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8213,6 +8258,7 @@
           <t>narrateur|Maya rejoint le doudou, après la sieste et la cuisine. Ça sent le savon des mains. On ouvre les mains, loin de l'autre. Maya dit pardon. Elle propose un geste. La peine reste un peu. On n'oblige pas l'amitié. Maman reste près. Maya dit merci à maman. Papa sourit. On gardu geste.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8380,6 +8426,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8547,6 +8594,7 @@
           <t>narrateur|Maya a choisi le jardin, après la sieste. La corde de la balançoire bouge. Maya choisit le jardin. Papa n'est pas loin. Maya dit pardon. Elle propose un geste. La peine reste un peu. On n'oblige pas l'amitié. Maman reste près.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8738,6 +8786,7 @@
           <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8905,6 +8954,7 @@
           <t>narrateur|Maya rejoint le ballon rouge, après la sieste et le jardin. Une feuille tourne et tombe. On s'assoit près de l'adulte. Maya dit pardon. Elle propose un geste. La peine reste un peu. On n'oblige pas l'amitié. Maman reste près. On laisse le ballon rouge à sa place. Maya est près de maman. Papa et maman sont là.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9072,6 +9122,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9239,6 +9290,7 @@
           <t>narrateur|Maya rejoint le seau bleu, après la sieste et le jardin. L'eau fait un tout petit bruit. On nomme ce qu'on sent. Maya dit pardon. Elle propose un geste. La peine reste un peu. On n'oblige pas l'amitié. Maman reste près. On laisse le seau bleu à sa place. Maya est près de maman. On respire.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9406,6 +9458,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9573,6 +9626,7 @@
           <t>narrateur|Maya rejoint le doudou, après la sieste et le jardin. Le soleil chauffe un peu le nez. On reprend le jeu, plus calme. Maya dit pardon. Elle propose un geste. La peine reste un peu. On n'oblige pas l'amitié. Maman reste près. On laisse le doudou à sa place. Maya est près de maman. Merci, et au dodo bientôt.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9740,6 +9794,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9909,6 +9964,7 @@
 narrateur|Maya dit pardon. Elle propose un geste. La peine reste un peu. On n'oblige pas l'amitié. Maman reste près.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10100,6 +10156,7 @@
           <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10267,6 +10324,7 @@
           <t>narrateur|Maya rejoint le ballon rouge, après la sieste et la chambre. Une plume vole. On range les chaussures. Maya dit pardon. Elle propose un geste. La peine reste un peu. On n'oblige pas l'amitié. Maman reste près. Maya boit une gorgée. Elle se sent plus légère. Le jeu peut recommencer.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10434,6 +10492,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10601,6 +10660,7 @@
           <t>narrateur|Maya rejoint le seau bleu, après la sieste et la chambre. Le pain croustille. On met le doudou près de soi. Maya dit pardon. Elle propose un geste. La peine reste un peu. On n'oblige pas l'amitié. Maman reste près. Maya boit une gorgée. Elle se sent plus légère. On se serre un peu.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10768,6 +10828,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10935,6 +10996,7 @@
           <t>narrateur|Maya rejoint le doudou, après la sieste et la chambre. La laine du doudou est douce. On écoute le cœur, tout doux. Maya dit pardon. Elle propose un geste. La peine reste un peu. On n'oblige pas l'amitié. Maman reste près. Maya boit une gorgée. Elle se sent plus légère. On rentre.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11102,6 +11164,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11269,6 +11332,7 @@
           <t>narrateur|Le soir, un doudou glisse du lit. Voilà le soir. La fenêtre tremble un tout petit peu. Maya pose les pieds par terre, près de maman. Maya dit pardon. Elle propose un geste. La peine reste un peu. On n'oblige pas l'amitié. Maman reste près.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11452,6 +11516,7 @@
           <t>narrateur|Après une bêtise, que dit-on ? Avec le soir.</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11623,6 +11688,7 @@
           <t>narrateur|Oui. Maya dit pardon. Elle propose un geste. La peine reste un peu. On n'oblige pas l'amitié. Maman reste près. Maya pose les pieds par terre. On continue, tout calme.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11814,6 +11880,7 @@
           <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11983,6 +12050,7 @@
 narrateur|Maya dit pardon. Elle propose un geste. La peine reste un peu. On n'oblige pas l'amitié. Maman reste près.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12174,6 +12242,7 @@
           <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12341,6 +12410,7 @@
           <t>narrateur|Maya rejoint le ballon rouge, après le soir et la cuisine. Un galet est lisse dans la main. On secoue les mains, loin. Maya dit pardon. Elle propose un geste. La peine reste un peu. On n'oblige pas l'amitié. Maman reste près. Maya serre la main de maman, tout doux. La journée continue, tout doux.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12508,6 +12578,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12675,6 +12746,7 @@
           <t>narrateur|Maya rejoint le seau bleu, après le soir et la cuisine. Le train souffle au loin. On pose le sac. Maya dit pardon. Elle propose un geste. La peine reste un peu. On n'oblige pas l'amitié. Maman reste près. Maya boit une gorgée. Elle se sent plus légère. On se dit à plus tard.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12842,6 +12914,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13011,6 +13084,7 @@
 narrateur|Le soleil est encore là.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13178,6 +13252,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13345,6 +13420,7 @@
           <t>narrateur|Maya a choisi le jardin, après le soir. Le sable est un peu frais. Le jardin reste à sa place. Maya aussi. Maya dit pardon. Elle propose un geste. La peine reste un peu. On n'oblige pas l'amitié. Maman reste près.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13536,6 +13612,7 @@
           <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13703,6 +13780,7 @@
           <t>narrateur|Maya rejoint le ballon rouge, après le soir et le jardin. Un grillon chante, tout petit. On invite d'une petite voix. Maya dit pardon. Elle propose un geste. La peine reste un peu. On n'oblige pas l'amitié. Maman reste près. Maya pose le ballon rouge et va vers maman. On gardu geste.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13870,6 +13948,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14037,6 +14116,7 @@
           <t>narrateur|Maya rejoint le seau bleu, après le soir et le jardin. Le bois de la table est lisse. On attend la réponse. Maya dit pardon. Elle propose un geste. La peine reste un peu. On n'oblige pas l'amitié. Maman reste près. Maya range le seau bleu un instant. Puis elle reprend, calme. Papa et maman sont là.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14204,6 +14284,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14371,6 +14452,7 @@
           <t>narrateur|Maya rejoint le doudou, après le soir et le jardin. Une goutte tombe dans l'évier. On propose une autre idée. Maya dit pardon. Elle propose un geste. La peine reste un peu. On n'oblige pas l'amitié. Maman reste près. On écoute le silence une seconde. Maya est assise. On respire.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14538,6 +14620,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14705,6 +14788,7 @@
           <t>narrateur|Maya a choisi la chambre, après le soir. Ça sent le savon de maman. Maya range un peu autour de la chambre. Elle respire. Maya dit pardon. Elle propose un geste. La peine reste un peu. On n'oblige pas l'amitié. Maman reste près.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14896,6 +14980,7 @@
           <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15063,6 +15148,7 @@
           <t>narrateur|Maya rejoint le ballon rouge, après le soir et la chambre. Le toboggan est un peu froid. On va vers papa ou maman. Maya dit pardon. Elle propose un geste. La peine reste un peu. On n'oblige pas l'amitié. Maman reste près. Maya dit merci à maman. Papa sourit. Merci, et au dodo bientôt.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15230,6 +15316,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15397,6 +15484,7 @@
           <t>narrateur|Maya rejoint le seau bleu, après le soir et la chambre. La clochette de la porte tinte. On dit stop, tout clair. Maya dit pardon. Elle propose un geste. La peine reste un peu. On n'oblige pas l'amitié. Maman reste près. On laisse le seau bleu à sa place. Maya est près de maman. Le jeu peut recommencer.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15564,6 +15652,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15731,6 +15820,7 @@
           <t>narrateur|Maya rejoint le doudou, après le soir et la chambre. Ça sent le thym du jardin. On s'éloigne d'un pas. Maya dit pardon. Elle propose un geste. La peine reste un peu. On n'oblige pas l'amitié. Maman reste près. Maya serre la main de maman, tout doux. On se serre un peu.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15898,6 +15988,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15916,7 +16007,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15940,6 +16031,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -15954,7 +16059,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16141,6 +16246,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
